--- a/src/main/resources/templates/excel/formatoIngresanteMuestraLab.xlsx
+++ b/src/main/resources/templates/excel/formatoIngresanteMuestraLab.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AE17C2-0AFB-4306-89AA-13977F482316}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{EF59EB06-4FB5-AD4F-A25B-D43F60D60F00}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="460" windowWidth="23260" windowHeight="12580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,19 +20,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>UNIVERSIDAD NACIONAL AGRARIA LA MOLINA</t>
   </si>
   <si>
     <t>CENTRO MÉDICO</t>
+  </si>
+  <si>
+    <t>CICLO ACADEMICO 2018-II</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>MATRICULA</t>
+  </si>
+  <si>
+    <t>APELLIDOS Y NOMBRES</t>
+  </si>
+  <si>
+    <t>RELACIÓN TOTAL DE ALUMNOS - LABORATORIO BIOANÁLISIS</t>
+  </si>
+  <si>
+    <t>FECHA TURNO</t>
+  </si>
+  <si>
+    <t>FECHA MUESTRA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,6 +77,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -71,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -79,21 +108,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -123,9 +225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>135890</xdr:rowOff>
+      <xdr:colOff>737858</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -155,7 +257,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="274320" y="0"/>
-          <a:ext cx="693420" cy="699770"/>
+          <a:ext cx="882638" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -430,91 +532,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="3" max="3" width="67" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+    <row r="2" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
+    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:15" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:M2"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="C4:M4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="124" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
